--- a/productos/02-presupuesto-mensual/Presupuesto-Mensual.xlsx
+++ b/productos/02-presupuesto-mensual/Presupuesto-Mensual.xlsx
@@ -131,7 +131,7 @@
     <t xml:space="preserve">8. Celdas protegidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Contraseña de desprotección: plantilla2026.</t>
+    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Si necesitas editar otra celda, ve a Revisar → Desproteger hoja (no pide contraseña).</t>
   </si>
   <si>
     <t xml:space="preserve">Soporte y otras plantillas de esta línea de productos: www.tumarca.com</t>
@@ -1856,11 +1856,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="19292548"/>
-        <c:axId val="58579816"/>
+        <c:axId val="36305862"/>
+        <c:axId val="25269834"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="19292548"/>
+        <c:axId val="36305862"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1892,7 +1892,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58579816"/>
+        <c:crossAx val="25269834"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1900,7 +1900,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="58579816"/>
+        <c:axId val="25269834"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1942,7 +1942,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19292548"/>
+        <c:crossAx val="36305862"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2334,11 +2334,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="77603257"/>
-        <c:axId val="60888678"/>
+        <c:axId val="63518889"/>
+        <c:axId val="23352891"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="77603257"/>
+        <c:axId val="63518889"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2370,7 +2370,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="60888678"/>
+        <c:crossAx val="23352891"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2378,7 +2378,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="60888678"/>
+        <c:axId val="23352891"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2420,7 +2420,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77603257"/>
+        <c:crossAx val="63518889"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2922,7 +2922,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="16">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:F6"/>
@@ -3073,7 +3073,7 @@
       <c r="C28" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="18">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
@@ -3254,7 +3254,7 @@
       <c r="D16" s="20"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B16:D16"/>
@@ -3378,7 +3378,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4166,7 +4166,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="1">
     <mergeCell ref="A2:N2"/>
   </mergeCells>
@@ -4711,7 +4711,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="1">
     <mergeCell ref="A2:N2"/>
   </mergeCells>
@@ -5385,7 +5385,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="4">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B3:F3"/>
@@ -5489,7 +5489,7 @@
       <c r="I7" s="41"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="10">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
